--- a/PRESUPUESTO-IA-INFRA-MONGODB.xlsx
+++ b/PRESUPUESTO-IA-INFRA-MONGODB.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escenarios" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parametros" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leeme" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bare-metal" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,10 +28,10 @@
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="&quot;US$ &quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;S/ &quot;#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="&quot;US$ &quot;#,##0.000000"/>
-    <numFmt numFmtId="168" formatCode="&quot;US$ &quot;#,##0.0000"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="&quot;US$ &quot;#,##0.000000"/>
+    <numFmt numFmtId="167" formatCode="&quot;US$ &quot;#,##0.0000"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -137,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,7 +177,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,13 +186,13 @@
     <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -200,10 +201,10 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -215,7 +216,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,7 +228,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -239,16 +240,16 @@
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -257,10 +258,10 @@
     <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -275,10 +276,61 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="169" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -949,14 +1001,1377 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="68" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>¿Y si en vez de nube alquilamos un servidor dedicado?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Análisis de reliablesite.net contra el modelo de Huawei de este mismo libro · precios de lista consultados el 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>A · DÓNDE SE VA HOY EL DINERO DE INFRAESTRUCTURA (del resto de este libro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Bloque de Huawei</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Qué es</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>US$/mes</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>¿Lo absorbe un servidor dedicado?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Cómputo</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>ECS 4 vCPU/8 GB + disco de sistema</t>
+        </is>
+      </c>
+      <c r="D6" s="5">
+        <f>Infraestructura!$K$5+Infraestructura!$K$6</f>
+        <v/>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>SÍ, y sobrado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>RDS PostgreSQL nodo único + 40 GB</t>
+        </is>
+      </c>
+      <c r="D7" s="5">
+        <f>Infraestructura!$K$7+Infraestructura!$K$8</f>
+        <v/>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>SÍ, pero pasa a ser Postgres administrado por usted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Almacenamiento</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>EVS 100 GB + OBS + CBR</t>
+        </is>
+      </c>
+      <c r="D8" s="5">
+        <f>Infraestructura!$K$10+Infraestructura!$K$11+Infraestructura!$K$12+Infraestructura!$K$13</f>
+        <v/>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>EL DISCO SÍ. El OBS conviene CONSERVARLO: es el respaldo fuera del servidor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>EIP + 30 GB de tráfico saliente</t>
+        </is>
+      </c>
+      <c r="D9" s="5">
+        <f>Infraestructura!$K$14+Infraestructura!$K$15</f>
+        <v/>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>SÍ. El ancho de banda pasa a ser fijo y sin medidor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Operación</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>LTS, CES, DNS, SCM, DAS</t>
+        </is>
+      </c>
+      <c r="D10" s="5">
+        <f>Infraestructura!$K$16+Infraestructura!$K$17+Infraestructura!$K$18+Infraestructura!$K$19+Infraestructura!$K$20</f>
+        <v/>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>NO del todo: logs y alarmas se autogestionan (netdata, uptime-kuma) o se pagan aparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Ingesta</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>ECS con GPU 1 h/trimestre</t>
+        </is>
+      </c>
+      <c r="D11" s="5">
+        <f>Infraestructura!$K$21</f>
+        <v/>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>SÍ, y mejor: hay servidores con GPU fija por US$ 189.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Instancia para Open Food Facts (opción A)</t>
+        </is>
+      </c>
+      <c r="D12" s="5">
+        <f>'MongoDB-OFF'!$E$89</f>
+        <v/>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>SÍ, y es donde más se gana: la RAM deja de ser el límite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL ADDRESABLE POR UN SERVIDOR DEDICADO</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr"/>
+      <c r="D13" s="8">
+        <f>SUM(D6:D12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="28" t="inlineStr">
+        <is>
+          <t>Es la cifra contra la que hay que comparar. NO incluye el consumo de IA (US$ 20/mes de ModelArts MaaS), que se paga igual desde donde sea que corra la aplicación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>B · CATÁLOGO DE RELIABLESITE — los candidatos que sirven para esto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Servidor</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Especificación</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>US$/mes lista</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>12 meses −20 %</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>24 meses −40 %</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Sede</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>ECC</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Por qué entra o por qué no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Intel Special 64 GB</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>4 núcleos · 64 GB DDR4 · 2×2 TB SSD</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>85</v>
+      </c>
+      <c r="E17" s="5">
+        <f>D17*0.8</f>
+        <v/>
+      </c>
+      <c r="F17" s="5">
+        <f>D17*0.6</f>
+        <v/>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>NY / Miami</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Sí (DDR4 reg.)</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>El más barato que aún sirve. Solo 4 núcleos y SSD SATA, no NVMe: la generación del PDF y la carga de Mongo van más lentas. Es el suelo, no la recomendación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>AMD Ryzen 3700X</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>8 núcleos · 64 GB DDR4 · 2×512 GB NVMe</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="n">
+        <v>119</v>
+      </c>
+      <c r="E18" s="5">
+        <f>D18*0.8</f>
+        <v/>
+      </c>
+      <c r="F18" s="5">
+        <f>D18*0.6</f>
+        <v/>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>DOS discos: permite RAID 1 por software, que es lo que evita que una avería de disco sea una restauración. 64 GB aguantan Open Food Facts COMPLETO más bge-m3. La opción barata sensata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>AMD Ryzen 5950X</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>16 núcleos · 128 GB DDR4 · 2 TB NVMe</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="n">
+        <v>179</v>
+      </c>
+      <c r="E19" s="5">
+        <f>D19*0.8</f>
+        <v/>
+      </c>
+      <c r="F19" s="5">
+        <f>D19*0.6</f>
+        <v/>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="H19" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Margen de sobra para todo a la vez, incluso reindexar embeddings en CPU sin tocar la API. Un solo disco: el RAID hay que comprarlo aparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>AMD Epyc 4545P</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>16 núcleos · 128 GB DDR5 ECC · 2 TB NVMe</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="n">
+        <v>199</v>
+      </c>
+      <c r="E20" s="5">
+        <f>D20*0.8</f>
+        <v/>
+      </c>
+      <c r="F20" s="5">
+        <f>D20*0.6</f>
+        <v/>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>LA RECOMENDADA. Chip de servidor con memoria ECC: en una máquina que sostiene la base de datos institucional, la corrección de errores de memoria no es un lujo, es lo que separa un servidor de un PC de escritorio caro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Epyc 4545P 256 GB</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>16 núcleos · 256 GB DDR5 ECC · 4 TB NVMe</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="n">
+        <v>279</v>
+      </c>
+      <c r="E21" s="5">
+        <f>D21*0.8</f>
+        <v/>
+      </c>
+      <c r="F21" s="5">
+        <f>D21*0.6</f>
+        <v/>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>NY / Ámsterdam / México</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>La única vía a la sede de QUERÉTARO, que es la más cercana a Perú del catálogo. Si la latencia o el 'estar en Latinoamérica' pesan en la decisión, esta es la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>nVidia Quadro RTX 4000</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>8 núcleos · 64 GB · 2×1 TB NVMe · GPU</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="n">
+        <v>189</v>
+      </c>
+      <c r="E22" s="5">
+        <f>D22*0.8</f>
+        <v/>
+      </c>
+      <c r="F22" s="5">
+        <f>D22*0.6</f>
+        <v/>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Los Ángeles</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Resuelve un problema que hoy no está resuelto: la ingesta de embeddings vive en un portátil personal. Con GPU fija, reindexar 29.054 productos son 15-30 min en vez de 2-3 h, y deja de depender de una máquina que puede no estar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="67" t="inlineStr">
+        <is>
+          <t>Los descuentos por prepago —10 % a 6 meses, 20 % a 12 y 40 % a 24— vienen del propio proveedor. Confirme antes de comprometer: cuota de alta, número de IPv4 incluidas, el escalón de ancho de banda que trae de serie y el precio del almacenamiento de respaldo. Son las cuatro cosas que no aparecen en la tabla de precios pública.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>C · LA COMPARACIÓN QUE IMPORTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="3" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Huawei (hoy)</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>RS · Ryzen 3700X</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>RS · Epyc 4545P</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>RS · Epyc + prepago 12m</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Servidor / cómputo y bases</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="5">
+        <f>$D$13</f>
+        <v/>
+      </c>
+      <c r="E28" s="5">
+        <f>D18</f>
+        <v/>
+      </c>
+      <c r="F28" s="5">
+        <f>D20</f>
+        <v/>
+      </c>
+      <c r="G28" s="5">
+        <f>E20</f>
+        <v/>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>En Huawei son cuatro servicios (ECS, RDS, EVS, instancia de Mongo). En bare metal es una sola máquina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>OBS para respaldo externo</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>SE CONSERVA a propósito. Un bucket de Huawei con el volcado de Postgres, el snapshot y los PDFs cuesta céntimos y hace que la avería del servidor no sea una pérdida de datos. Es lo que quita el miedo al bare metal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>DNS y certificado</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Cloudflare gratuito o la zona de Huawei. Let's Encrypt para el TLS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Logs, métricas y alarmas</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>netdata y uptime-kuma en el propio servidor: cero de coste y una tarde de trabajo. Lo que se pierde es la integración con la consola.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr"/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>COSTE MENSUAL TOTAL</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr"/>
+      <c r="D32" s="8">
+        <f>SUM(D28:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="8">
+        <f>SUM(E28:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="8">
+        <f>SUM(F28:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="8">
+        <f>SUM(G28:G31)</f>
+        <v/>
+      </c>
+      <c r="I32" s="28" t="inlineStr">
+        <is>
+          <t>Comparable línea a línea con el bloque A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr"/>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Ahorro frente a Huawei (US$/mes)</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr"/>
+      <c r="D33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="11">
+        <f>$D$32-E32</f>
+        <v/>
+      </c>
+      <c r="F33" s="11">
+        <f>$D$32-F32</f>
+        <v/>
+      </c>
+      <c r="G33" s="11">
+        <f>$D$32-G32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr"/>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Ahorro frente a Huawei (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr"/>
+      <c r="D34" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="68">
+        <f>E33/$D$32</f>
+        <v/>
+      </c>
+      <c r="F34" s="68">
+        <f>F33/$D$32</f>
+        <v/>
+      </c>
+      <c r="G34" s="68">
+        <f>G33/$D$32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Ahorro ANUAL (US$)</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr"/>
+      <c r="D35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="11">
+        <f>E33*12</f>
+        <v/>
+      </c>
+      <c r="F35" s="11">
+        <f>F33*12</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
+        <f>G33*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>D · LO QUE SE COMPRA CON ESE DINERO — capacidad, no solo precio</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="3" t="inlineStr"/>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Recurso</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Huawei (hoy)</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>RS · Ryzen 3700X</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>RS · Epyc 4545P</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Qué desbloquea</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Núcleos de CPU</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G39" s="64">
+        <f>F39/D39</f>
+        <v/>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Huawei son 10 vCPU repartidos en tres máquinas (4 del ECS + 2 del RDS + 4 del nodo Mongo), y una vCPU es medio núcleo físico. Los 16 del Epyc son núcleos reales sin vecinos ruidosos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr"/>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>RAM total (GB)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="E40" s="29" t="n">
+        <v>64</v>
+      </c>
+      <c r="F40" s="29" t="n">
+        <v>128</v>
+      </c>
+      <c r="G40" s="64">
+        <f>F40/D40</f>
+        <v/>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>AQUÍ ESTÁ LA HISTORIA. Los 20 GB de Huawei van repartidos y obligan a la proyección P1 de Open Food Facts. Con 64 o 128 GB el working set completo de los 4,68 M de productos (12,2 GB) entra sin discusión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Disco (GB)</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr"/>
+      <c r="D41" s="29" t="n">
+        <v>240</v>
+      </c>
+      <c r="E41" s="29" t="n">
+        <v>1024</v>
+      </c>
+      <c r="F41" s="29" t="n">
+        <v>2048</v>
+      </c>
+      <c r="G41" s="64">
+        <f>F41/D41</f>
+        <v/>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Y es NVMe local, no un volumen de red. La carga de MongoDB y la generación de PDF son sensibles a esto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Salida de red (GB/mes)</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F42" s="29" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G42" s="64">
+        <f>F42/D42</f>
+        <v/>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>En Huawei cada GB de salida se factura a US$ 0,09; aquí el ancho de banda es fijo y sin medidor. Hoy da igual —son 30 GB— pero el día que el CITE publique el acceso a sus asociados, deja de dar igual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="48" customHeight="1">
+      <c r="A44" s="47" t="inlineStr">
+        <is>
+          <t>EL DESBLOQUEO REAL · Con 64-128 GB de RAM, la proyección P1 de la hoja MongoDB-OFF deja de ser necesaria. Se importa Open Food Facts ENTERO —los 1.066 campos, la nutrición, el eco-score, todo— y sigue sobrando memoria. Eso no es un ahorro: es una capacidad que hoy el producto no tiene, y que en Huawei costaría subir el nodo a la opción B (US$ 130/mes más). Comparado a IGUAL capacidad, el servidor dedicado no ahorra un 15 %: ahorra del orden del 60 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>E · LO QUE SE PIERDE, CON SU MITIGACIÓN Y LO QUE CUESTA MITIGARLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="3" t="inlineStr"/>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Lo que desaparece</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Por qué duele</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Gravedad</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Mitigación y coste</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr"/>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>Residencia del dato</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>La decisión de INFRA-HUAWEI-CLOUD.md §1 justificó Huawei en parte por 'residencia del dato: la región contratada'. Miami y Nueva York son jurisdicción de EE. UU.</t>
+        </is>
+      </c>
+      <c r="D48" s="48" t="inlineStr">
+        <is>
+          <t>BLOQUEANTE si existe el requisito</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>No se mitiga: se pregunta. Si el CITE exige que el dato viva en Perú o prohíbe EE. UU., la conversación termina aquí y hay que optimizar dentro de Huawei. Querétaro (México) es lo más cercano del catálogo y tampoco es Perú.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr"/>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>RDS gestionado: backup diario y PITR</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Hoy Huawei hace la copia y la recuperación a un punto en el tiempo. En bare metal lo hace usted.</t>
+        </is>
+      </c>
+      <c r="D49" s="69" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>pgBackRest o pg_dump nocturno contra el bucket OBS que se conserva (US$ 1,50/mes). Es una tarde de trabajo y un cron. LA CONDICIÓN INNEGOCIABLE: probar una restauración real antes de confiar en ella. Un respaldo sin verificar no es un respaldo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr"/>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Hardware replicado por debajo</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>El EVS de Huawei está replicado; un NVMe suelto no. Si muere el disco, muere el disco.</t>
+        </is>
+      </c>
+      <c r="D50" s="69" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>Elegir un servidor con DOS discos y montar RAID 1 por software, que el proveedor incluye. Los modelos 3700X y Epyc 256 GB lo traen; el 5950X y el Epyc 128 GB vienen con un solo disco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr"/>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Elasticidad y apagar entre ensayos</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>En Huawei se apaga el ECS entre ensayos y se paga solo lo encendido. Un servidor dedicado se paga entero los 30 días, se use o no.</t>
+        </is>
+      </c>
+      <c r="D51" s="69" t="inlineStr">
+        <is>
+          <t>Alta AHORA, nula después</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>No hay mitigación: es una propiedad del modelo. Por eso la recomendación de abajo dice que HOY el bare metal es más caro, no más barato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr"/>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Redimensionar en cinco minutos</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Subir de 8 a 16 GB en Huawei es un reinicio. En bare metal es cambiar de contrato y migrar.</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>Se compensa comprando de más desde el principio: con 128 GB no hay que redimensionar en años. Es justo lo que hace asequible el bare metal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>IAM, agencias y gestión de secretos</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>El ECS tomaba credenciales temporales del servicio de metadatos, sin AK/SK en disco.</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>Vuelve el fichero .env con chmod 600 y claves de larga vida para el bucket. Es un retroceso de seguridad real, aunque acotado: la superficie es una máquina, no una flota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr"/>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Consola, DAS, LTS, CES</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Consultar la base desde el navegador, ver logs y recibir alarmas venía hecho.</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>netdata + uptime-kuma + un contenedor de pgAdmin: coste cero, una tarde de trabajo, y funciona igual de bien a esta escala.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr"/>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Contratación institucional</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Un CITE puede necesitar factura formal, contrato y un proveedor con presencia en Perú. Huawei tiene canal de socios; un proveedor de bare metal estadounidense se contrata con tarjeta.</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>Preguntar a administración ANTES de decidir por técnica. Es la clase de requisito que aparece al final y tumba la decisión entera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>F · LATENCIA — lo que hay que medir, no suponer</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="3" t="inlineStr"/>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Tramo</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Desde Santiago (Huawei)</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Desde Miami</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Desde Querétaro</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr"/>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Usuario de Lima o Trujillo → aplicación</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>40-60 ms</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>70-90 ms</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>80-110 ms</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>El único tramo que el usuario nota: lo paga CADA clic de la SPA. Los 40-60 ms de Santiago están documentados en INFRA-HUAWEI-CLOUD.md §2; los otros dos son órdenes de magnitud del enrutado habitual desde Perú y HAY QUE MEDIRLOS, no darlos por buenos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Aplicación → base de datos</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>&lt; 2 ms</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>&lt; 0,1 ms</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>&lt; 0,1 ms</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>A FAVOR DEL BARE METAL, y no es menor: en una sola máquina la base es un socket local. El riesgo R1 del plan de S3 —'8-12 viajes a Postgres por run'— desaparece del todo, no se reduce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr"/>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Aplicación → ModelArts MaaS (Singapur)</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>~300 ms</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>~250 ms</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>~270 ms</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>Prácticamente indiferente: se paga una vez por etapa sobre generaciones de 15-123 s medidas. Es ruido en los tres casos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="44" customHeight="1">
+      <c r="A64" s="67" t="inlineStr">
+        <is>
+          <t>CÓMO MEDIRLO ANTES DE DECIDIR, y cuesta una hora: alquile el servidor más barato del catálogo por un mes (US$ 49), y desde una conexión de Lima mida el RTT p95 contra él y contra el ECS de Huawei. El proyecto ya tiene definido este método —es el gate de INFRA-HUAWEI-CLOUD.md §2— y el número resultante decide el punto de la latencia sin discusión. Cincuenta dólares para no basar una decisión de dos años en una suposición es barato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>G · RECOMENDACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="52" customHeight="1">
+      <c r="A67" s="33" t="inlineStr">
+        <is>
+          <t>1. NO CAMBIAR ANTES DEL CDR DEL 28 DE AGOSTO, y el motivo es aritmético, no prudencial. Hasta el CDR el escenario correcto es el A —encender la máquina solo para ensayar—, y eso cuesta US$ 65 al mes en Huawei. Un servidor dedicado se paga los 30 días completos: HOY el bare metal es MÁS CARO, no más barato. Además, cambiar de infraestructura a cuatro semanas de una revisión de diseño, con la migración de Supabase a RDS todavía sin escribir (13,5-15 h medidas), es comprar riesgo a cambio de nada en esa fecha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="52" customHeight="1">
+      <c r="A68" s="33" t="inlineStr">
+        <is>
+          <t>2. HAY UNA SOLA PREGUNTA QUE DECIDE ESTO, Y NO ES TÉCNICA: ¿exige el CITE que el dato resida en Perú, o prohíbe alojarlo en Estados Unidos? Si la respuesta es sí, el análisis termina: hay que quedarse en Huawei y optimizar dentro (compromiso anual, −35 %; escenario A hasta el piloto). El propio documento de infraestructura dejó esto por escrito: 'si el requisito de residencia existe, el precio está justificado; si no existe, conviene saber que se está pagando por él'. Esta es la ocasión de averiguarlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="52" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>3. SI NO HAY REQUISITO DE RESIDENCIA, el bare metal gana con claridad a partir del momento en que el servicio está encendido 24×7. El candidato es el AMD Epyc 4545P (16 núcleos, 128 GB DDR5 con ECC, 2 TB NVMe, Miami) a US$ 199 de lista, o el Ryzen 3700X (8 núcleos, 64 GB, dos discos NVMe para RAID 1) a US$ 119 si el presupuesto aprieta. Con prepago de 12 meses la factura cae otro 20 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="52" customHeight="1">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>4. EL ARGUMENTO FUERTE NO ES EL AHORRO, ES LA CAPACIDAD. A precio de lista el ahorro es modesto. Pero la comparación honesta no es máquina contra máquina: es que en Huawei los 20 GB de RAM repartidos OBLIGAN a importar Open Food Facts proyectado, y en una máquina de 128 GB se importa entero y sobra memoria. A igual capacidad —es decir, subiendo el nodo de Mongo a la opción B, US$ 130 más— el servidor dedicado ahorra del orden del 60 % y encima corre en núcleos reales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="52" customHeight="1">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>5. NO ES 'TODO O NADA': CONSERVE EL BUCKET OBS. Un bucket de Huawei con el volcado de Postgres, el snapshot y los PDFs cuesta US$ 1,50 al mes y hace que la avería del servidor deje de ser una pérdida de datos. Es la pieza barata que convierte el bare metal de apuesta en decisión. La regla asociada es innegociable y ya está escrita en el plan: probar una restauración real antes de confiar en el respaldo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="52" customHeight="1">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>6. HAY UN PROBLEMA QUE EL BARE METAL RESUELVE Y LA NUBE NO ESTABA RESOLVIENDO: la ingesta de embeddings vive hoy en un portátil personal con una RTX 4060 — la única pieza del sistema que no está en ningún servidor y que nadie más puede reproducir. Un servidor con Quadro RTX 4000 cuesta US$ 189 al mes, que es caro para usarlo cuatro veces al año; pero si el servidor principal es de 16 núcleos, reindexar en CPU sin molestar a la API pasa a ser viable, y el portátil sale de la ruta crítica igual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="52" customHeight="1">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>7. LO QUE HAY QUE HACER ESTA SEMANA, en este orden: preguntar a administración si hay requisito de residencia y si se puede contratar a un proveedor estadounidense; y alquilar por un mes el servidor de US$ 49 para medir el RTT p95 desde Lima contra él y contra Huawei. Con esas dos respuestas la decisión se toma sola. Sin ellas, cualquier elección es una corazonada con hoja de cálculo.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A72:I72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1048,10 +2463,10 @@
           <t>En uso · etapas 1 y 2a</t>
         </is>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="53" t="n">
         <v>0.000135</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="53" t="n">
         <v>0.000539</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -1072,10 +2487,10 @@
           <t>En uso · etapas 3, 4 y 5</t>
         </is>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="53" t="n">
         <v>0.01</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="53" t="n">
         <v>0.02</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -1096,10 +2511,10 @@
           <t>NO DISPONIBLE (404)</t>
         </is>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="53" t="n">
         <v>0.000539</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="53" t="n">
         <v>0.002965</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -1120,10 +2535,10 @@
           <t>NO DISPONIBLE (404)</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="53" t="n">
         <v>0.003</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="53" t="n">
         <v>0.006</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -1213,19 +2628,19 @@
       <c r="E13" s="20" t="n">
         <v>548</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="54">
         <f>$D$6</f>
         <v/>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="54">
         <f>$E$6</f>
         <v/>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="55">
         <f>D13/1000*F13+E13/1000*G13</f>
         <v/>
       </c>
-      <c r="I13" s="23" t="n">
+      <c r="I13" s="56" t="n">
         <v>34.2</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -1256,19 +2671,19 @@
       <c r="E14" s="24" t="n">
         <v>400</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="54">
         <f>$D$6</f>
         <v/>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="54">
         <f>$E$6</f>
         <v/>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="55">
         <f>D14/1000*F14+E14/1000*G14</f>
         <v/>
       </c>
-      <c r="I14" s="23" t="n">
+      <c r="I14" s="56" t="n">
         <v>15.5</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
@@ -1299,16 +2714,16 @@
       <c r="E15" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="21" t="n">
+      <c r="G15" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="22" t="n">
+      <c r="H15" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="23" t="n">
+      <c r="I15" s="56" t="n">
         <v>0.2</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -1339,19 +2754,19 @@
       <c r="E16" s="20" t="n">
         <v>2004</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="54">
         <f>$D$7</f>
         <v/>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="54">
         <f>$E$7</f>
         <v/>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="55">
         <f>D16/1000*F16+E16/1000*G16</f>
         <v/>
       </c>
-      <c r="I16" s="23" t="n">
+      <c r="I16" s="56" t="n">
         <v>123.2</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
@@ -1382,19 +2797,19 @@
       <c r="E17" s="24" t="n">
         <v>1200</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="54">
         <f>$D$7</f>
         <v/>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="54">
         <f>$E$7</f>
         <v/>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="55">
         <f>D17/1000*F17+E17/1000*G17</f>
         <v/>
       </c>
-      <c r="I17" s="23" t="n">
+      <c r="I17" s="56" t="n">
         <v>30</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -1425,19 +2840,19 @@
       <c r="E18" s="24" t="n">
         <v>1400</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="54">
         <f>$D$7</f>
         <v/>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="54">
         <f>$E$7</f>
         <v/>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="55">
         <f>D18/1000*F18+E18/1000*G18</f>
         <v/>
       </c>
-      <c r="I18" s="23" t="n">
+      <c r="I18" s="56" t="n">
         <v>35</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
@@ -1468,16 +2883,16 @@
       <c r="E19" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="F19" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="21" t="n">
+      <c r="G19" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="22" t="n">
+      <c r="H19" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="23" t="n">
+      <c r="I19" s="56" t="n">
         <v>3</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
@@ -1504,11 +2919,11 @@
       </c>
       <c r="F21" s="9" t="inlineStr"/>
       <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="26">
+      <c r="H21" s="57">
         <f>SUM(H13:H16)</f>
         <v/>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="58">
         <f>SUM(I13:I16)</f>
         <v/>
       </c>
@@ -1536,11 +2951,11 @@
       </c>
       <c r="F22" s="9" t="inlineStr"/>
       <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="26">
+      <c r="H22" s="57">
         <f>SUM(H13:H19)</f>
         <v/>
       </c>
-      <c r="I22" s="27">
+      <c r="I22" s="58">
         <f>SUM(I13:I19)</f>
         <v/>
       </c>
@@ -1572,19 +2987,19 @@
       <c r="E23" s="24" t="n">
         <v>350</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="54">
         <f>$D$7</f>
         <v/>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="54">
         <f>$E$7</f>
         <v/>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="55">
         <f>(D23/1000*F23+E23/1000*G23)*3</f>
         <v/>
       </c>
-      <c r="I23" s="23" t="n">
+      <c r="I23" s="56" t="n">
         <v>60</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
@@ -1814,15 +3229,15 @@
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="31">
+      <c r="D33" s="59">
         <f>D32/(D27+D28)</f>
         <v/>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="59">
         <f>E32/(E27+E28)</f>
         <v/>
       </c>
-      <c r="F33" s="31">
+      <c r="F33" s="59">
         <f>F32/(F27+F28)</f>
         <v/>
       </c>
@@ -1909,7 +3324,7 @@
       <c r="C38" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="56">
         <f>C38/$H$22</f>
         <v/>
       </c>
@@ -1934,7 +3349,7 @@
       <c r="C39" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="56">
         <f>C39/$H$21</f>
         <v/>
       </c>
@@ -1959,7 +3374,7 @@
       <c r="C40" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="56">
         <f>C40/$H$22</f>
         <v/>
       </c>
@@ -1984,7 +3399,7 @@
       <c r="C41" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="56">
         <f>C41/$H$22</f>
         <v/>
       </c>
@@ -2058,15 +3473,15 @@
           <t>glm-5.2</t>
         </is>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="59">
         <f>$H$16</f>
         <v/>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="59">
         <f>$H$21</f>
         <v/>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="59">
         <f>$H$22</f>
         <v/>
       </c>
@@ -2093,15 +3508,15 @@
           <t>deepseek-v4-flash</t>
         </is>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="59">
         <f>$D$16/1000*$D$6+$E$16/1000*$E$6</f>
         <v/>
       </c>
-      <c r="E46" s="31">
+      <c r="E46" s="59">
         <f>$H$21-$H$16+D46</f>
         <v/>
       </c>
-      <c r="F46" s="31">
+      <c r="F46" s="59">
         <f>$H$22-$H$16+D46</f>
         <v/>
       </c>
@@ -2129,15 +3544,15 @@
           <t>glm-5.2</t>
         </is>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="59">
         <f>$D$16/2/1000*$D$7+$E$16/1000*$E$7</f>
         <v/>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="59">
         <f>$H$21-$H$16+D47</f>
         <v/>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="59">
         <f>$H$22-$H$16+D47</f>
         <v/>
       </c>
@@ -2165,15 +3580,15 @@
           <t>glm-5.0 — NO DISPONIBLE</t>
         </is>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="59">
         <f>$D$16/1000*$D$8+$E$16/1000*$E$8</f>
         <v/>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="59">
         <f>$H$21-$H$16+D48</f>
         <v/>
       </c>
-      <c r="F48" s="31">
+      <c r="F48" s="59">
         <f>$H$22-$H$16+D48</f>
         <v/>
       </c>
@@ -2971,13 +4386,13 @@
         <f>Parametros!$B$6</f>
         <v/>
       </c>
-      <c r="G5" s="35" t="n">
+      <c r="G5" s="60" t="n">
         <v>0.096</v>
       </c>
-      <c r="H5" s="35" t="n">
+      <c r="H5" s="60" t="n">
         <v>0.125</v>
       </c>
-      <c r="I5" s="35" t="n">
+      <c r="I5" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="J5" s="5">
@@ -3030,13 +4445,13 @@
       <c r="F6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="35" t="n">
+      <c r="G6" s="60" t="n">
         <v>0.1</v>
       </c>
-      <c r="H6" s="35" t="n">
+      <c r="H6" s="60" t="n">
         <v>0.12</v>
       </c>
-      <c r="I6" s="35" t="n">
+      <c r="I6" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="J6" s="5">
@@ -3090,13 +4505,13 @@
         <f>Parametros!$B$6</f>
         <v/>
       </c>
-      <c r="G7" s="35" t="n">
+      <c r="G7" s="60" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H7" s="35" t="n">
+      <c r="H7" s="60" t="n">
         <v>0.095</v>
       </c>
-      <c r="I7" s="35" t="n">
+      <c r="I7" s="60" t="n">
         <v>0.12</v>
       </c>
       <c r="J7" s="5">
@@ -3149,13 +4564,13 @@
       <c r="F8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="35" t="n">
+      <c r="G8" s="60" t="n">
         <v>0.15</v>
       </c>
-      <c r="H8" s="35" t="n">
+      <c r="H8" s="60" t="n">
         <v>0.18</v>
       </c>
-      <c r="I8" s="35" t="n">
+      <c r="I8" s="60" t="n">
         <v>0.22</v>
       </c>
       <c r="J8" s="5">
@@ -3208,13 +4623,13 @@
       <c r="F9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="35" t="n">
+      <c r="G9" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="35" t="n">
+      <c r="H9" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="35" t="n">
+      <c r="I9" s="60" t="n">
         <v>3</v>
       </c>
       <c r="J9" s="5">
@@ -3267,13 +4682,13 @@
       <c r="F10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="35" t="n">
+      <c r="G10" s="60" t="n">
         <v>0.1</v>
       </c>
-      <c r="H10" s="35" t="n">
+      <c r="H10" s="60" t="n">
         <v>0.12</v>
       </c>
-      <c r="I10" s="35" t="n">
+      <c r="I10" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="J10" s="5">
@@ -3326,13 +4741,13 @@
       <c r="F11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="35" t="n">
+      <c r="G11" s="60" t="n">
         <v>0.019</v>
       </c>
-      <c r="H11" s="35" t="n">
+      <c r="H11" s="60" t="n">
         <v>0.024</v>
       </c>
-      <c r="I11" s="35" t="n">
+      <c r="I11" s="60" t="n">
         <v>0.03</v>
       </c>
       <c r="J11" s="5">
@@ -3385,13 +4800,13 @@
       <c r="F12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="35" t="n">
+      <c r="G12" s="60" t="n">
         <v>0.5</v>
       </c>
-      <c r="H12" s="35" t="n">
+      <c r="H12" s="60" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="35" t="n">
+      <c r="I12" s="60" t="n">
         <v>2</v>
       </c>
       <c r="J12" s="5">
@@ -3444,13 +4859,13 @@
       <c r="F13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="35" t="n">
+      <c r="G13" s="60" t="n">
         <v>0.05</v>
       </c>
-      <c r="H13" s="35" t="n">
+      <c r="H13" s="60" t="n">
         <v>0.06</v>
       </c>
-      <c r="I13" s="35" t="n">
+      <c r="I13" s="60" t="n">
         <v>0.08</v>
       </c>
       <c r="J13" s="5">
@@ -3504,13 +4919,13 @@
         <f>Parametros!$B$6</f>
         <v/>
       </c>
-      <c r="G14" s="35" t="n">
+      <c r="G14" s="60" t="n">
         <v>0.005</v>
       </c>
-      <c r="H14" s="35" t="n">
+      <c r="H14" s="60" t="n">
         <v>0.007</v>
       </c>
-      <c r="I14" s="35" t="n">
+      <c r="I14" s="60" t="n">
         <v>0.01</v>
       </c>
       <c r="J14" s="5">
@@ -3564,13 +4979,13 @@
         <f>Parametros!$B$14</f>
         <v/>
       </c>
-      <c r="G15" s="35" t="n">
+      <c r="G15" s="60" t="n">
         <v>0.08</v>
       </c>
-      <c r="H15" s="35" t="n">
+      <c r="H15" s="60" t="n">
         <v>0.09</v>
       </c>
-      <c r="I15" s="35" t="n">
+      <c r="I15" s="60" t="n">
         <v>0.12</v>
       </c>
       <c r="J15" s="5">
@@ -3623,13 +5038,13 @@
       <c r="F16" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="35" t="n">
+      <c r="G16" s="60" t="n">
         <v>0.3</v>
       </c>
-      <c r="H16" s="35" t="n">
+      <c r="H16" s="60" t="n">
         <v>0.4</v>
       </c>
-      <c r="I16" s="35" t="n">
+      <c r="I16" s="60" t="n">
         <v>0.5</v>
       </c>
       <c r="J16" s="5">
@@ -3682,13 +5097,13 @@
       <c r="F17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="35" t="n">
+      <c r="G17" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="35" t="n">
+      <c r="H17" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="35" t="n">
+      <c r="I17" s="60" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="5">
@@ -3741,13 +5156,13 @@
       <c r="F18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="35" t="n">
+      <c r="G18" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="35" t="n">
+      <c r="H18" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="35" t="n">
+      <c r="I18" s="60" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="5">
@@ -3800,13 +5215,13 @@
       <c r="F19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="35" t="n">
+      <c r="G19" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="35" t="n">
+      <c r="H19" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="35" t="n">
+      <c r="I19" s="60" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5">
@@ -3859,13 +5274,13 @@
       <c r="F20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="35" t="n">
+      <c r="G20" s="60" t="n">
         <v>0.5</v>
       </c>
-      <c r="H20" s="35" t="n">
+      <c r="H20" s="60" t="n">
         <v>0.5</v>
       </c>
-      <c r="I20" s="35" t="n">
+      <c r="I20" s="60" t="n">
         <v>0.5</v>
       </c>
       <c r="J20" s="5">
@@ -3918,13 +5333,13 @@
       <c r="F21" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="35" t="n">
+      <c r="G21" s="60" t="n">
         <v>0.5</v>
       </c>
-      <c r="H21" s="35" t="n">
+      <c r="H21" s="60" t="n">
         <v>0.7</v>
       </c>
-      <c r="I21" s="35" t="n">
+      <c r="I21" s="60" t="n">
         <v>1.5</v>
       </c>
       <c r="J21" s="5">
@@ -4741,7 +6156,7 @@
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="39" t="n">
+      <c r="D23" s="61" t="n">
         <v>0.402</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -4797,7 +6212,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="40">
+      <c r="D27" s="62">
         <f>D10/D14</f>
         <v/>
       </c>
@@ -4820,7 +6235,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="40">
+      <c r="D28" s="62">
         <f>D8/D6</f>
         <v/>
       </c>
@@ -4866,7 +6281,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr"/>
-      <c r="D30" s="42">
+      <c r="D30" s="63">
         <f>D17/D29</f>
         <v/>
       </c>
@@ -5029,10 +6444,10 @@
           <t>único</t>
         </is>
       </c>
-      <c r="D38" s="45" t="n">
+      <c r="D38" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="39" t="n">
+      <c r="E38" s="61" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="29">
@@ -5061,10 +6476,10 @@
           <t>multiclave</t>
         </is>
       </c>
-      <c r="D39" s="45" t="n">
+      <c r="D39" s="64" t="n">
         <v>1.2</v>
       </c>
-      <c r="E39" s="39" t="n">
+      <c r="E39" s="61" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="29">
@@ -5093,10 +6508,10 @@
           <t>multiclave</t>
         </is>
       </c>
-      <c r="D40" s="45" t="n">
+      <c r="D40" s="64" t="n">
         <v>6.5</v>
       </c>
-      <c r="E40" s="39" t="n">
+      <c r="E40" s="61" t="n">
         <v>0.467</v>
       </c>
       <c r="F40" s="29">
@@ -5125,10 +6540,10 @@
           <t>multiclave</t>
         </is>
       </c>
-      <c r="D41" s="45" t="n">
+      <c r="D41" s="64" t="n">
         <v>25.3</v>
       </c>
-      <c r="E41" s="39" t="n">
+      <c r="E41" s="61" t="n">
         <v>0.402</v>
       </c>
       <c r="F41" s="29">
@@ -5157,10 +6572,10 @@
           <t>multiclave</t>
         </is>
       </c>
-      <c r="D42" s="45" t="n">
+      <c r="D42" s="64" t="n">
         <v>2.1</v>
       </c>
-      <c r="E42" s="39" t="n">
+      <c r="E42" s="61" t="n">
         <v>0.32</v>
       </c>
       <c r="F42" s="29">
@@ -5189,10 +6604,10 @@
           <t>multiclave</t>
         </is>
       </c>
-      <c r="D43" s="45" t="n">
+      <c r="D43" s="64" t="n">
         <v>2.3</v>
       </c>
-      <c r="E43" s="39" t="n">
+      <c r="E43" s="61" t="n">
         <v>0.402</v>
       </c>
       <c r="F43" s="29">
@@ -5221,10 +6636,10 @@
           <t>simple</t>
         </is>
       </c>
-      <c r="D44" s="45" t="n">
+      <c r="D44" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="39" t="n">
+      <c r="E44" s="61" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="29">
@@ -5253,10 +6668,10 @@
           <t>texto</t>
         </is>
       </c>
-      <c r="D45" s="45" t="n">
+      <c r="D45" s="64" t="n">
         <v>40</v>
       </c>
-      <c r="E45" s="39" t="n">
+      <c r="E45" s="61" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="F45" s="29">
@@ -5624,7 +7039,7 @@
       <c r="C66" s="29" t="n">
         <v>3297</v>
       </c>
-      <c r="D66" s="46" t="n">
+      <c r="D66" s="65" t="n">
         <v>0.158</v>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -5643,7 +7058,7 @@
       <c r="C67" s="29" t="n">
         <v>3075</v>
       </c>
-      <c r="D67" s="46" t="n">
+      <c r="D67" s="65" t="n">
         <v>0.147</v>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -5662,7 +7077,7 @@
       <c r="C68" s="29" t="n">
         <v>1740</v>
       </c>
-      <c r="D68" s="46" t="n">
+      <c r="D68" s="65" t="n">
         <v>0.083</v>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -5681,7 +7096,7 @@
       <c r="C69" s="29" t="n">
         <v>1256</v>
       </c>
-      <c r="D69" s="46" t="n">
+      <c r="D69" s="65" t="n">
         <v>0.06</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -5700,7 +7115,7 @@
       <c r="C70" s="29" t="n">
         <v>1254</v>
       </c>
-      <c r="D70" s="46" t="n">
+      <c r="D70" s="65" t="n">
         <v>0.06</v>
       </c>
       <c r="E70" s="30" t="inlineStr">
@@ -5719,7 +7134,7 @@
       <c r="C71" s="29" t="n">
         <v>1081</v>
       </c>
-      <c r="D71" s="46" t="n">
+      <c r="D71" s="65" t="n">
         <v>0.052</v>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -5738,7 +7153,7 @@
       <c r="C72" s="29" t="n">
         <v>930</v>
       </c>
-      <c r="D72" s="46" t="n">
+      <c r="D72" s="65" t="n">
         <v>0.044</v>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -5757,7 +7172,7 @@
       <c r="C73" s="29" t="n">
         <v>735</v>
       </c>
-      <c r="D73" s="46" t="n">
+      <c r="D73" s="65" t="n">
         <v>0.035</v>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -5776,7 +7191,7 @@
       <c r="C74" s="29" t="n">
         <v>519</v>
       </c>
-      <c r="D74" s="46" t="n">
+      <c r="D74" s="65" t="n">
         <v>0.025</v>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -5795,7 +7210,7 @@
       <c r="C75" s="29" t="n">
         <v>515</v>
       </c>
-      <c r="D75" s="46" t="n">
+      <c r="D75" s="65" t="n">
         <v>0.025</v>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -5814,7 +7229,7 @@
       <c r="C76" s="29" t="n">
         <v>123</v>
       </c>
-      <c r="D76" s="46" t="n">
+      <c r="D76" s="65" t="n">
         <v>0.006</v>
       </c>
       <c r="E76" s="30" t="inlineStr">
@@ -6468,13 +7883,13 @@
           <t>4 vCPU · 8 GB · General computing-plus</t>
         </is>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="60" t="n">
         <v>0.096</v>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="60" t="n">
         <v>0.125</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -6499,13 +7914,13 @@
           <t>8 vCPU · 32 GB — nodo de MongoDB, opción B</t>
         </is>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="60" t="n">
         <v>0.38</v>
       </c>
-      <c r="D6" s="35" t="n">
+      <c r="D6" s="60" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="60" t="n">
         <v>0.62</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -6530,13 +7945,13 @@
           <t>rds.pg.n1.large.2 · 2 vCPU/4 GB · nodo único</t>
         </is>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="60" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="60" t="n">
         <v>0.095</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="60" t="n">
         <v>0.12</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -6561,13 +7976,13 @@
           <t>dds.mongodb.s6.xlarge.4.repset · 4 vCPU/16 GB · POR NODO</t>
         </is>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="60" t="n">
         <v>0.28</v>
       </c>
-      <c r="D8" s="35" t="n">
+      <c r="D8" s="60" t="n">
         <v>0.4</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="60" t="n">
         <v>0.53</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -6592,13 +8007,13 @@
           <t>Volumen de datos</t>
         </is>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="60" t="n">
         <v>0.1</v>
       </c>
-      <c r="D9" s="35" t="n">
+      <c r="D9" s="60" t="n">
         <v>0.12</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="60" t="n">
         <v>0.15</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -6623,13 +8038,13 @@
           <t>SSD en la nube</t>
         </is>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="60" t="n">
         <v>0.15</v>
       </c>
-      <c r="D10" s="35" t="n">
+      <c r="D10" s="60" t="n">
         <v>0.18</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="60" t="n">
         <v>0.22</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -6654,13 +8069,13 @@
           <t>Almacenamiento de objetos</t>
         </is>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="60" t="n">
         <v>0.019</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="60" t="n">
         <v>0.024</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="60" t="n">
         <v>0.03</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -6685,13 +8100,13 @@
           <t>Bóveda de respaldo</t>
         </is>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="60" t="n">
         <v>0.05</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="60" t="n">
         <v>0.06</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="60" t="n">
         <v>0.08</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -6716,13 +8131,13 @@
           <t>IP elástica asociada</t>
         </is>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="60" t="n">
         <v>0.005</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="60" t="n">
         <v>0.007</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="60" t="n">
         <v>0.01</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -6747,13 +8162,13 @@
           <t>Egress</t>
         </is>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="60" t="n">
         <v>0.08</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="60" t="n">
         <v>0.09</v>
       </c>
-      <c r="E14" s="35" t="n">
+      <c r="E14" s="60" t="n">
         <v>0.12</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -6778,13 +8193,13 @@
           <t>Retención 7 días</t>
         </is>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="60" t="n">
         <v>0.3</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="60" t="n">
         <v>0.4</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="60" t="n">
         <v>0.5</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -6809,13 +8224,13 @@
           <t>1 zona alojada</t>
         </is>
       </c>
-      <c r="C16" s="35" t="n">
+      <c r="C16" s="60" t="n">
         <v>0.5</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="60" t="n">
         <v>0.5</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="60" t="n">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -6840,13 +8255,13 @@
           <t>Alarmas, consola SQL, certificado</t>
         </is>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="60" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -7227,15 +8642,15 @@
           <t>Costo por consulta (todo incluido)</t>
         </is>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="59">
         <f>B14/MAX(B5+B6,1)</f>
         <v/>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="59">
         <f>C14/MAX(C5+C6,1)</f>
         <v/>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="59">
         <f>D14/MAX(D5+D6,1)</f>
         <v/>
       </c>
@@ -7430,7 +8845,7 @@
           <t>Impuestos aplicables</t>
         </is>
       </c>
-      <c r="B9" s="51" t="n">
+      <c r="B9" s="66" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -7450,7 +8865,7 @@
           <t>Descuento por compromiso anual</t>
         </is>
       </c>
-      <c r="B10" s="51" t="n">
+      <c r="B10" s="66" t="n">
         <v>0.35</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -7510,7 +8925,7 @@
           <t>Tasa de acierto del cache</t>
         </is>
       </c>
-      <c r="B13" s="39" t="n">
+      <c r="B13" s="61" t="n">
         <v>0.514</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -7576,8 +8991,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="12" t="inlineStr">
         <is>
@@ -7641,7 +9054,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="B15" s="12" t="inlineStr">
         <is>
@@ -7677,7 +9089,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="B21" s="12" t="inlineStr">
         <is>
@@ -7713,7 +9124,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="B27" s="12" t="inlineStr">
         <is>
@@ -7770,7 +9180,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="B36" s="12" t="inlineStr">
         <is>
